--- a/data/trans_orig/P5_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>26113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47156</t>
+          <t>46835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60033</t>
+          <t>60183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82790</t>
+          <t>81843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64674</t>
+          <t>63636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80239</t>
+          <t>79096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88449</t>
+          <t>88064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140709</t>
+          <t>141656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163466</t>
+          <t>163316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>37140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38043</t>
+          <t>39248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56197</t>
+          <t>56314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64849</t>
+          <t>66249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89005</t>
+          <t>88256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87051</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102202</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84545</t>
+          <t>84428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102699</t>
+          <t>101494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176702</t>
+          <t>177451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200858</t>
+          <t>199458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>35850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42113</t>
+          <t>42276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>60814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72903</t>
+          <t>71998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86695</t>
+          <t>87002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81244</t>
+          <t>81826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95548</t>
+          <t>95382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158776</t>
+          <t>159606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178307</t>
+          <t>178144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41360</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62049</t>
+          <t>62566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>30413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>47782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76298</t>
+          <t>77373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103643</t>
+          <t>105444</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103287</t>
+          <t>102770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123976</t>
+          <t>123421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108855</t>
+          <t>109164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126655</t>
+          <t>126533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218639</t>
+          <t>216838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245984</t>
+          <t>244909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125887</t>
+          <t>124435</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158034</t>
+          <t>156383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130804</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162956</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264926</t>
+          <t>265693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311705</t>
+          <t>313158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345325</t>
+          <t>346976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377472</t>
+          <t>378924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365593</t>
+          <t>362507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397745</t>
+          <t>395653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>718750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766982</t>
+          <t>766215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25558</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>50391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>64514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87387</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55201</t>
+          <t>56269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71571</t>
+          <t>72438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61455</t>
+          <t>62110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79303</t>
+          <t>79143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122242</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145130</t>
+          <t>145115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31332</t>
+          <t>31503</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47873</t>
+          <t>47956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>36426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55501</t>
+          <t>55680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72830</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97201</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81110</t>
+          <t>81027</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97651</t>
+          <t>97480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99055</t>
+          <t>98876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118056</t>
+          <t>118130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186338</t>
+          <t>184419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210709</t>
+          <t>209414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>26846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41552</t>
+          <t>42675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31718</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>62535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85729</t>
+          <t>84779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63299</t>
+          <t>62176</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78478</t>
+          <t>78005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>68331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85066</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135905</t>
+          <t>136855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159158</t>
+          <t>159099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64501</t>
+          <t>64239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84985</t>
+          <t>84760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66788</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87843</t>
+          <t>87730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138702</t>
+          <t>136644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166201</t>
+          <t>167645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,71%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>61242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81501</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>67211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>89283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134742</t>
+          <t>133298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162241</t>
+          <t>164299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>164635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>199619</t>
+          <t>199800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186550</t>
+          <t>189494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224109</t>
+          <t>224900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>362249</t>
+          <t>360875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412672</t>
+          <t>412380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>277346</t>
+          <t>277165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>312330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314672</t>
+          <t>313881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352231</t>
+          <t>349287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>603074</t>
+          <t>603366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>653497</t>
+          <t>654871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40387</t>
+          <t>39860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48364</t>
+          <t>48585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>60627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84030</t>
+          <t>82544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>50225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>64620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56310</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110729</t>
+          <t>112215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133746</t>
+          <t>134132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,87%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37242</t>
+          <t>37656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55513</t>
+          <t>56144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51229</t>
+          <t>52149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71773</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94875</t>
+          <t>93993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121083</t>
+          <t>121339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96414</t>
+          <t>95783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114685</t>
+          <t>114271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103530</t>
+          <t>102961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124074</t>
+          <t>123154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206147</t>
+          <t>205891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>232355</t>
+          <t>233237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>33338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49625</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40490</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58503</t>
+          <t>58442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79274</t>
+          <t>77661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>101567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66927</t>
+          <t>67335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82541</t>
+          <t>83214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>74405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92357</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145171</t>
+          <t>147832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170125</t>
+          <t>171738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>53616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74113</t>
+          <t>73913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>54054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73505</t>
+          <t>73746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111013</t>
+          <t>110996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140377</t>
+          <t>140439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91546</t>
+          <t>91746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112854</t>
+          <t>112043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84703</t>
+          <t>84462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105174</t>
+          <t>104154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183491</t>
+          <t>183429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212855</t>
+          <t>212872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166203</t>
+          <t>166664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>201377</t>
+          <t>201612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193596</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231374</t>
+          <t>232148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369934</t>
+          <t>371768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>423452</t>
+          <t>424218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322846</t>
+          <t>322611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>358020</t>
+          <t>357559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339659</t>
+          <t>338885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>377437</t>
+          <t>374790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671804</t>
+          <t>671038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>725322</t>
+          <t>723488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103570</t>
+          <t>103903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113187</t>
+          <t>113311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126628</t>
+          <t>126063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137099</t>
+          <t>136994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235244</t>
+          <t>235197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248617</t>
+          <t>248571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22312</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40315</t>
+          <t>39140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35336</t>
+          <t>36794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44611</t>
+          <t>43679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69785</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>150197</t>
+          <t>151372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>168330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219699</t>
+          <t>218241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237204</t>
+          <t>236779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>375763</t>
+          <t>376681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400937</t>
+          <t>401869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110417</t>
+          <t>113804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>44615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60603</t>
+          <t>61505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164982</t>
+          <t>167811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79984</t>
+          <t>76597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161847</t>
+          <t>162330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141500</t>
+          <t>140671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160602</t>
+          <t>159809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210705</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315084</t>
+          <t>314182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39954</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59333</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52732</t>
+          <t>51707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75912</t>
+          <t>75437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98137</t>
+          <t>97689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129330</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107212</t>
+          <t>106198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126591</t>
+          <t>125902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104383</t>
+          <t>104858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>128588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217510</t>
+          <t>218552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>248703</t>
+          <t>249151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113404</t>
+          <t>111726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>213673</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111905</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149274</t>
+          <t>151459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>237586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348796</t>
+          <t>342996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>459514</t>
+          <t>451065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551334</t>
+          <t>553012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>611754</t>
+          <t>609569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>649123</t>
+          <t>650407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1076971</t>
+          <t>1082771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1186447</t>
+          <t>1188181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38018</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30113</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46577</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33298</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26113</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41573</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25775</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40880</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38018</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>30225</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46835</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>59470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81843</t>
+          <t>82809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80271</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71712</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88176</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>74,54%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>71911</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63636</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79096</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64329</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79434</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80271</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71454</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>88064</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>67,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141656</t>
+          <t>140690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163316</t>
+          <t>164029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47290</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38099</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55859</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>29470</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22016</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37140</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22765</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36938</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>47290</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39248</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>56314</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,6%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66249</t>
+          <t>65130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88256</t>
+          <t>88443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93452</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84883</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>102643</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>95495</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>87825</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>102949</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>88027</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>102200</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>76,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93452</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>84428</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>101494</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177451</t>
+          <t>177264</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199458</t>
+          <t>200577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23567</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16817</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30796</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27494</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20846</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35850</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21254</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>34531</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>23567</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>17191</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>30747</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42276</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60814</t>
+          <t>61275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>89006</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81777</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95756</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80354</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71998</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>87002</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>73317</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86594</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>74,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>89006</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81826</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95382</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159606</t>
+          <t>159145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178144</t>
+          <t>178907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,17%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38772</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30725</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47337</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51193</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41915</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>62566</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41346</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>61402</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38772</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30413</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>47782</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77373</t>
+          <t>76758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>104799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>118174</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>109609</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>126221</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>114143</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>102770</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>123421</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>103934</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>123990</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>69,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>118174</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>109164</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>126533</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>75,3%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216838</t>
+          <t>217483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244909</t>
+          <t>245524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>131055</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>164091</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>24,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>141455</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>124435</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>156383</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>126371</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>157231</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>132896</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>166042</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>265693</t>
+          <t>265826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313158</t>
+          <t>312670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>380902</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>364458</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>397494</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>72,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>75,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>361904</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>346976</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>378924</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>346128</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>376988</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>71,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>380902</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>362507</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>395653</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>718750</t>
+          <t>719238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766215</t>
+          <t>766082</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34057</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51362</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33569</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24691</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40860</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26139</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42355</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33358</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50391</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64514</t>
+          <t>64333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88099</t>
+          <t>87399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70350</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61139</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78444</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>63560</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56269</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72438</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54774</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70990</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70350</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62110</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>79143</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,53%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121530</t>
+          <t>122230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145115</t>
+          <t>145296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46076</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37512</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55998</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>39351</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31503</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47956</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31794</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48317</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,51%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>46076</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36426</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>55680</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>73493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>97193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108480</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98558</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>117044</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>89632</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81027</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>97480</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80666</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>97189</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108480</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>98876</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>118130</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,19%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184419</t>
+          <t>186346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209414</t>
+          <t>210046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,08%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40473</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32611</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49213</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33953</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26846</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42675</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26692</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41812</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>40473</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>31775</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>48453</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62535</t>
+          <t>63143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84779</t>
+          <t>87348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76311</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67571</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84173</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70898</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62176</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78005</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63039</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78159</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76311</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68331</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136855</t>
+          <t>134286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159099</t>
+          <t>158491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>77443</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67344</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>88067</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>56,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>74535</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>64239</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>84760</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>63998</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85030</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>51,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>44,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>58,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>77443</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>65658</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>87730</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136644</t>
+          <t>136697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167645</t>
+          <t>165375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>77498</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66874</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>87597</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>50,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>71467</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61242</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>81763</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60972</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>82004</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>48,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>41,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>77498</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>67211</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>89283</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>50,02%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>135568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164299</t>
+          <t>164246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>188165</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>225055</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>164635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>199800</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>164366</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199035</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>189494</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>224900</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>360875</t>
+          <t>363763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412380</t>
+          <t>411236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>332639</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>313726</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>350616</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>295557</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>277165</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>312330</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>277930</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>312599</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>58,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>332639</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>313881</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>349287</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>61,74%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>603366</t>
+          <t>604510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>654871</t>
+          <t>651983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40122</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31520</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49030</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32440</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25465</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39860</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25396</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39690</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31644</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48585</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,33%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>61892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82544</t>
+          <t>84337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64552</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55644</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73154</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57645</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50225</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64620</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50395</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>64689</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64552</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56089</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73030</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,67%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112215</t>
+          <t>110422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134132</t>
+          <t>132867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61310</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51257</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>71739</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>46541</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37656</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56144</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38614</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>56155</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61310</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>52149</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72342</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93993</t>
+          <t>94542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121339</t>
+          <t>120305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>113993</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>103564</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>124046</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>105386</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95783</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>114271</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95772</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>113313</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>113993</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>102961</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>123154</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205891</t>
+          <t>206925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233237</t>
+          <t>232688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49041</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39886</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57403</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41594</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33338</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49217</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>33979</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49914</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>35,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>49041</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>40129</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58442</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,92%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77661</t>
+          <t>80232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101567</t>
+          <t>104298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83806</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75444</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>92961</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>56,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>74958</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67335</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83214</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66638</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>82573</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>64,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83806</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>74405</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>92718</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>63,08%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147832</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>171738</t>
+          <t>169167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62920</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52608</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>72791</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>62888</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>53616</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73913</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>53457</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>75353</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>37,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>62920</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>54054</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>73746</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110996</t>
+          <t>110555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140439</t>
+          <t>142031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>95288</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>85417</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>105600</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>102771</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>91746</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>90306</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>112202</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>62,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>95288</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84462</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>104154</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183429</t>
+          <t>181837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212872</t>
+          <t>213313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165659</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165659</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165659</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,74 +5989,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>195913</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>233758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>183462</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>166664</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>201612</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>165689</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>201641</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>38,46%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>196243</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>232148</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>591</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371768</t>
+          <t>372034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424218</t>
+          <t>420792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>357639</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>337275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>375120</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>512</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>340761</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322611</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>357559</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322582</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>358534</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>61,54%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>357639</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>338885</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>374790</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671038</t>
+          <t>674464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>723488</t>
+          <t>723222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>789</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>524223</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>524223</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>524223</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6719</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3016</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12811</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7627</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13377</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119187</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113095</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122890</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>109653</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>103903</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>113311</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,5%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>133226</t>
+          <t>113194</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126063</t>
+          <t>107383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136994</t>
+          <t>116906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>242880</t>
+          <t>232381</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235197</t>
+          <t>224690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248571</t>
+          <t>237978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24433</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17420</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33703</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>30143</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22182</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39140</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55915</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43679</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68867</t>
+          <t>66077</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212773</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203503</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219786</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>160369</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>151372</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>168330</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>229263</t>
+          <t>154532</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218241</t>
+          <t>145435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236779</t>
+          <t>162249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>389633</t>
+          <t>367305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376681</t>
+          <t>355542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401869</t>
+          <t>378954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30777</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22697</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41230</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>53362</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28071</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>113804</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>29244</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>21585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44615</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>87265</t>
+          <t>60021</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61505</t>
+          <t>48309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167811</t>
+          <t>73638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137564</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127111</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145644</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>137039</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76597</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>162330</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>71,97%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151383</t>
+          <t>127806</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140671</t>
+          <t>117592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159809</t>
+          <t>135465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>288422</t>
+          <t>265370</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207876</t>
+          <t>251753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314182</t>
+          <t>277082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59615</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49068</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70103</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>49937</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40643</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>60347</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51707</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75437</t>
+          <t>59416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113294</t>
+          <t>108244</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97689</t>
+          <t>94611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128288</t>
+          <t>123502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>108804</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>98316</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>119351</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>116608</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106198</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>125902</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>116938</t>
+          <t>118019</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104858</t>
+          <t>107232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128588</t>
+          <t>127165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>233546</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218552</t>
+          <t>211565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>249151</t>
+          <t>240456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121544</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>105481</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140487</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111726</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>213673</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110621</t>
+          <t>100715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151459</t>
+          <t>134229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>237175</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237586</t>
+          <t>214098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342996</t>
+          <t>263885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>578328</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>559385</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>594391</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>774</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>523669</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>451065</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>553012</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>630810</t>
+          <t>513551</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>609569</t>
+          <t>494953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>650407</t>
+          <t>528467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1154479</t>
+          <t>1091879</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1082771</t>
+          <t>1065169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1188181</t>
+          <t>1114956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
